--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775001</v>
+        <v>121775000</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>57508</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,26 +1719,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1824,10 +1824,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121775000</v>
+        <v>121775001</v>
       </c>
       <c r="B11" t="n">
-        <v>57508</v>
+        <v>57510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,26 +1840,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -1703,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775000</v>
+        <v>121775001</v>
       </c>
       <c r="B10" t="n">
-        <v>57508</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,26 +1719,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1824,10 +1824,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121775001</v>
+        <v>121775000</v>
       </c>
       <c r="B11" t="n">
-        <v>57510</v>
+        <v>57508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1840,26 +1840,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121775001</v>
+        <v>121775000</v>
       </c>
       <c r="B10" t="n">
-        <v>57527</v>
+        <v>57525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1719,26 +1719,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1821,127 +1821,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>121775000</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57525</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103020</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Entita</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Poecile palustris</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1822,6 +1822,849 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127329773</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56523</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Endast 1 ganska svag inspelning.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127329258</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56544</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127329213</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56532</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127329237</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56539</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127329947</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57459</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127329269</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56525</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127329484</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56531</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Endast en inspelning/passage. Finns dammar borta vid campingen (1 km bort) men inte just där inspelningen gjordes.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>127329773</v>
       </c>
       <c r="B11" t="n">
-        <v>56523</v>
+        <v>56527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127329258</v>
       </c>
       <c r="B12" t="n">
-        <v>56544</v>
+        <v>56548</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127329213</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
+        <v>56536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127329237</v>
       </c>
       <c r="B14" t="n">
-        <v>56539</v>
+        <v>56543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>127329947</v>
       </c>
       <c r="B15" t="n">
-        <v>57459</v>
+        <v>57463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>127329269</v>
       </c>
       <c r="B16" t="n">
-        <v>56525</v>
+        <v>56529</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>127329484</v>
       </c>
       <c r="B17" t="n">
-        <v>56531</v>
+        <v>56535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>127329773</v>
       </c>
       <c r="B11" t="n">
-        <v>56527</v>
+        <v>56529</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127329258</v>
       </c>
       <c r="B12" t="n">
-        <v>56548</v>
+        <v>56550</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127329213</v>
       </c>
       <c r="B13" t="n">
-        <v>56536</v>
+        <v>56538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127329237</v>
       </c>
       <c r="B14" t="n">
-        <v>56543</v>
+        <v>56545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>127329947</v>
       </c>
       <c r="B15" t="n">
-        <v>57463</v>
+        <v>57465</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>127329269</v>
       </c>
       <c r="B16" t="n">
-        <v>56529</v>
+        <v>56531</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>127329484</v>
       </c>
       <c r="B17" t="n">
-        <v>56535</v>
+        <v>56537</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>127329773</v>
       </c>
       <c r="B11" t="n">
-        <v>56529</v>
+        <v>56532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127329258</v>
       </c>
       <c r="B12" t="n">
-        <v>56550</v>
+        <v>56553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127329213</v>
       </c>
       <c r="B13" t="n">
-        <v>56538</v>
+        <v>56541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127329237</v>
       </c>
       <c r="B14" t="n">
-        <v>56545</v>
+        <v>56548</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>127329947</v>
       </c>
       <c r="B15" t="n">
-        <v>57465</v>
+        <v>57468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>127329269</v>
       </c>
       <c r="B16" t="n">
-        <v>56531</v>
+        <v>56534</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>127329484</v>
       </c>
       <c r="B17" t="n">
-        <v>56537</v>
+        <v>56540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>127329773</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>56538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>127329258</v>
       </c>
       <c r="B12" t="n">
-        <v>56553</v>
+        <v>56559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>127329213</v>
       </c>
       <c r="B13" t="n">
-        <v>56541</v>
+        <v>56547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127329237</v>
       </c>
       <c r="B14" t="n">
-        <v>56548</v>
+        <v>56554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>127329947</v>
       </c>
       <c r="B15" t="n">
-        <v>57468</v>
+        <v>57474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>127329269</v>
       </c>
       <c r="B16" t="n">
-        <v>56534</v>
+        <v>56540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>127329484</v>
       </c>
       <c r="B17" t="n">
-        <v>56540</v>
+        <v>56546</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1822,849 +1822,6 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>127329773</v>
-      </c>
-      <c r="B11" t="n">
-        <v>56538</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100015</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Barbastell</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Barbastella barbastellus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Endast 1 ganska svag inspelning.</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>127329258</v>
-      </c>
-      <c r="B12" t="n">
-        <v>56559</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pipistrellus pygmaeus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S12" t="n">
-        <v>50</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>22:12</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>22:12</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>127329213</v>
-      </c>
-      <c r="B13" t="n">
-        <v>56547</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Myotis daubentonii</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S13" t="n">
-        <v>50</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>22:01</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>22:01</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>127329237</v>
-      </c>
-      <c r="B14" t="n">
-        <v>56554</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Nyctalus noctula</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S14" t="n">
-        <v>50</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>22:03</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>22:03</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>127329947</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57474</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>102118</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nattskärra</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Caprimulgus europaeus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S15" t="n">
-        <v>50</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>127329269</v>
-      </c>
-      <c r="B16" t="n">
-        <v>56540</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Eptesicus nilssonii</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S16" t="n">
-        <v>50</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>22:12</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>22:12</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127329484</v>
-      </c>
-      <c r="B17" t="n">
-        <v>56546</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100086</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Dammfladdermus</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Myotis dasycneme</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(F.Boie, 1825)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>ultraljudsdetektor</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Gamla Vägen, Skruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>521912</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6280756</v>
-      </c>
-      <c r="S17" t="n">
-        <v>50</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Lessebo</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Ljuder</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>22:28</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>22:28</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Endast en inspelning/passage. Finns dammar borta vid campingen (1 km bort) men inte just där inspelningen gjordes.</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Björn Dellming</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18960-2021 artfynd.xlsx
+++ b/artfynd/A 18960-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1822,6 +1822,849 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127329773</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56538</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Endast 1 ganska svag inspelning.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127329258</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56559</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127329213</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56547</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127329237</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56554</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>22:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127329947</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57474</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127329269</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56540</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127329484</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56546</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100086</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dammfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Myotis dasycneme</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(F.Boie, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ultraljudsdetektor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gamla Vägen, Skruv, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>521912</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6280756</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lessebo</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ljuder</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>22:28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Endast en inspelning/passage. Finns dammar borta vid campingen (1 km bort) men inte just där inspelningen gjordes.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Björn Dellming</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
